--- a/results/summary_all_datasets.xlsx
+++ b/results/summary_all_datasets.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6629</v>
+        <v>0.7298</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5592</v>
+        <v>0.6348</v>
       </c>
     </row>
     <row r="3">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8298</v>
+        <v>0.9019</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7114</v>
+        <v>0.8216</v>
       </c>
     </row>
   </sheetData>
